--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
-    <t xml:space="preserve">Punitaqui</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:40</t>
+    <t xml:space="preserve">2026-09-09 22:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
@@ -664,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:26</t>
+    <t xml:space="preserve">2026-09-12 19:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -57,12 +57,12 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
+    <t xml:space="preserve">Ovalle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Ovalle</t>
-  </si>
-  <si>
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:43</t>
+    <t xml:space="preserve">2026-09-24 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -647,7 +647,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4304</v>
+        <v>4301</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2019</v>
@@ -664,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4301</v>
+        <v>4304</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2019</v>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:20</t>
+    <t xml:space="preserve">2026-09-27 22:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:09</t>
+    <t xml:space="preserve">2026-10-01 20:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:50</t>
+    <t xml:space="preserve">2026-10-02 13:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:16</t>
+    <t xml:space="preserve">2026-10-04 08:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2019_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:02</t>
+    <t xml:space="preserve">2026-10-05 07:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
